--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,217 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Development (Python)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0de03440ff246ea3</t>
+      <c r="D10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Django</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=353dfd37d6f98139</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa98384834f1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,112 +741,357 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Django</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353dfd37d6f98139</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Sr. Java Developer with Payments – R01564829</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Lime</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>11.1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Senior Engineer - Payments Modernization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a3aa5caeb20f8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Sr. Java Developer with Payments – R01564829</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,322 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78cb4d11caed672c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Senior Engineer</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>GEICO</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D26" t="n">
         <v>10.4</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AtoZeeSolutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,147 +811,147 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tripledot Studios</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a3aa5caeb20f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,21 +1077,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78cb4d11caed672c</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,28 +517,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,46 +552,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb0d0f10975359</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Cloud Connectivity Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AtoZeeSolutions</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,112 +871,112 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AtoZeeSolutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,77 +1336,1197 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AWS Database Engineer / Cloud DBA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior GCP IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Java Developer with Payments – R01564829</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wellington Management</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Full stack</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kore.ai</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nova AI/ML Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RedCloud Consulting</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=718ee5bf46190c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nova AI/ML Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RedCloud Consulting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AWS Database Engineer / Cloud DBA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ellumen, Inc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Junior GCP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AWS Database Engineer / Cloud DBA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Glencore</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Senior Engineer</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>GEICO</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D59" t="n">
         <v>10.4</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cloud Support Associate</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abff269bbd7ee617</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer - Payments Modernization</t>
+          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Engineer</t>
+          <t>Senior Engineer - Payments Modernization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f7aa9808e3bc85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Cloud Disaster Recovery Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb0d0f10975359</t>
+          <t>https://www.indeed.com/viewjob?jk=eaeff5e1c81b908e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,81 +622,81 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
+          <t>https://www.indeed.com/viewjob?jk=a9bb0d0f10975359</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Connectivity Architect</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Senior Cloud Connectivity Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AtoZeeSolutions</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AtoZeeSolutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,84 +1161,84 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,46 +1252,46 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>Sr. Java Developer with Payments – R01564829</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718ee5bf46190c60</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ellumen, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Nova AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Ellumen, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,15 +2516,295 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Glencore</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cloud Support Associate</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=abff269bbd7ee617</t>
         </is>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9bb0d0f10975359</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Connectivity Architect</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Senior Cloud Connectivity Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,49 +1406,49 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d616d744010b2d4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,49 +1931,49 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Java Developer with Payments – R01564829</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Bickham Services Unlimited, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff60d7a3553e89e2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ellumen, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Odyssey Logistics &amp; Technology Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, MLflow, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2d55c2b18bdcbb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Ellumen, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Nova AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,15 +2796,435 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SYSTECH USA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Cloud Database Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AWS Database Engineer / Cloud DBA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Plymouth Rock Assurance</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist &amp; Modeler</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Iberdrola Group</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Glencore</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cloud Support Associate</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=abff269bbd7ee617</t>
         </is>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
+          <t>https://www.indeed.com/viewjob?jk=74f3191cc3d47286</t>
         </is>
       </c>
     </row>
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Scala, Oracle</t>
+          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>AI Application Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, Step Functions, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=171403dbdac6e42f</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Sr Platform &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, GCP, Vertex AI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Connectivity Architect</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, Azure, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,89 +881,89 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf91c86d1642dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Azure, Spark, PySpark, Scala, Kafka, Polars</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MS Excel</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,38 +972,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow</t>
+          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Microsoft SQL Server/ETL Developer w/SSIS experience [On-Site]</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93b9c004dc5445b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e129ef424b7bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AtoZeeSolutions</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d4500029e471c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,116 +1182,116 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=837e9f344d302e6d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58cf7cc708c832</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Oracle, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d616d744010b2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,49 +1616,49 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77c5c3760e672b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Sr. Java Developer with Payments – R01564829</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Developer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bickham Services Unlimited, LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff60d7a3553e89e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c9fcdbb30f98349</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,49 +2351,49 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>SmartAdvocate</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Data Scientist &amp; Modeler</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Odyssey Logistics &amp; Technology Corporation</t>
+          <t>Iberdrola Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2d55c2b18bdcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ellumen, Inc</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2be74f55bd39cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Scala, ETL, Tableau, MLOps, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16782d9fbfaff550</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,462 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>hatch IT</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SYSTECH USA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Cloud Database Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Iberdrola Group</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Orange, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Glencore</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Cloud Support Associate</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abff269bbd7ee617</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-11.xlsx
+++ b/results/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>NEXON America</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, DynamoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff92c7be8a4ed26f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
+          <t>https://www.indeed.com/viewjob?jk=cf763802f514ac89</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7c3880bf1468af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Engineer, Market Data New</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>MIO Partners</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, RDS, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ce8c2bb2e05265</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
+          <t>https://www.indeed.com/viewjob?jk=4d44f16ef92378b0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2be041ba7dd258</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Java Developer with Payments – R01564829</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, EMR, Lambda, API Gateway, Azure, Data Factory, Databricks, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AWS API Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
+          <t>https://www.indeed.com/viewjob?jk=b4249a3228aea17d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Java Developer with Payments – R01564829</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b028c72e4fead57</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3b2ea12351135</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, BigQuery, Scala, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=55dd6036cf4386c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full stack</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,104 +2026,104 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Engineer 2 - Full stack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a4c233ec9d2bd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, Flume, Spark, Scala, Kafka, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=8925c0b6808e2ef8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Business Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ADF &amp; Databricks</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f39f88a9b70f0a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
+          <t>Oracle, PostgreSQL, MongoDB, ETL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - ADF &amp; Databricks</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Serenity Healthcare</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f3a914de107c82</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, PostgreSQL, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Serenity Healthcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fffc235cb241e45</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ec2088a10dc04e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, BigQuery, Scala, Data Modeling, ETL, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f2031edb48e342e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SmartAdvocate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc004557d9736a0f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=490033b77e24b17c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>SmartAdvocate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Data Scientist &amp; Modeler</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Iberdrola Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, CI/CD, GitHub Actions, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0439c2a3373376b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,85 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>AWS, ECS, Azure, MLOps, CI/CD, Jenkins, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
         </is>
